--- a/master_data_template.xlsx
+++ b/master_data_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3657DB-FC4C-46A6-95DD-2BC986FB1459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B48AAF-DEFC-48F8-A60A-B6D1CB9B2E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Papers Master List" sheetId="1" r:id="rId1"/>

--- a/master_data_template.xlsx
+++ b/master_data_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B48AAF-DEFC-48F8-A60A-B6D1CB9B2E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26F05BD-C5B2-4265-81FD-37E3CC180898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Papers Master List" sheetId="1" r:id="rId1"/>
